--- a/Azure_Remediation_ReportT.xlsx
+++ b/Azure_Remediation_ReportT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50995E3E-469F-465F-9DFC-107765372E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D354FD4-303B-441C-89AA-4550EC937332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{710A899D-571A-4743-BB8E-066A6642D9AD}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Command Tier</t>
   </si>
   <si>
-    <t>Federal Agency / Branch</t>
-  </si>
-  <si>
     <t>Total Active Units</t>
   </si>
   <si>
@@ -83,12 +80,19 @@
   </si>
   <si>
     <t>Nissan Motor Co</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.0000000_);_(&quot;$&quot;* \(#,##0.0000000\);_(&quot;$&quot;* &quot;-&quot;???????_);_(@_)"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -677,17 +681,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -735,18 +741,7 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -763,6 +758,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.0000000_);_(&quot;$&quot;* \(#,##0.0000000\);_(&quot;$&quot;* &quot;-&quot;???????_);_(@_)"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -841,6 +837,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -848,18 +853,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -876,14 +884,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4427509F-B8B3-4BC5-9BF7-75C056438784}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4427509F-B8B3-4BC5-9BF7-75C056438784}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E13" xr:uid="{4427509F-B8B3-4BC5-9BF7-75C056438784}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{625F11CD-EEBE-4869-8353-A0895B828298}" name="Command Tier" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D9A15808-24F5-4846-AB2B-CFD8E13595E5}" name="Federal Agency / Branch" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{967908B7-A211-49A5-B467-1F05C9AC73BD}" name="Total Active Units" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6C1A4BD7-53F7-4A3B-9F57-376788401CDF}" name="Precise Unit Cost (MSRP)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{BBBABA60-92D6-4E03-8FEC-D11AD3AD279E}" name="Total Financial Footprint" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{625F11CD-EEBE-4869-8353-A0895B828298}" name="Command Tier" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D9A15808-24F5-4846-AB2B-CFD8E13595E5}" name="Agency" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{967908B7-A211-49A5-B467-1F05C9AC73BD}" name="Total Active Units" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6C1A4BD7-53F7-4A3B-9F57-376788401CDF}" name="Precise Unit Cost (MSRP)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BBBABA60-92D6-4E03-8FEC-D11AD3AD279E}" name="Total Financial Footprint" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1217,220 +1225,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>36448246</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="10">
         <v>25.1653671706263</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="8">
         <v>917233493.31531298</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>32971705</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="10">
         <v>25.5853398058252</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="8">
         <v>843592276.40242696</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>32751775</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="10">
         <v>25.407067307692301</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="8">
         <v>832126551.87139404</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>32063260</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="10">
         <v>25.689659781287901</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="8">
         <v>823694240.87897897</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>32443716</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="10">
         <v>25.377940119760499</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="8">
         <v>823354681.91051602</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>31822170</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="10">
         <v>25.521116333725001</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="8">
         <v>812137302.56157506</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>32880396</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="10">
         <v>24.688904761904698</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="8">
         <v>811780965.37771499</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>31853081</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="10">
         <v>25.444305210918099</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="8">
         <v>810479514.87209702</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1">
         <v>31460870</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="10">
         <v>25.372231707317098</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="8">
         <v>798232483.35378098</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>32202276</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="10">
         <v>24.683688029020502</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="8">
         <v>794870934.60841501</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1">
         <v>31532498</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="10">
         <v>25.038216482164799</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="8">
         <v>789517511.14742899</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="A13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="7">
         <v>29925570</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <v>24.544396014943899</v>
       </c>
       <c r="E13" s="9">
